--- a/BWI/bestwine_output/bestwine_Guatemala.xlsx
+++ b/BWI/bestwine_output/bestwine_Guatemala.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA62"/>
+  <dimension ref="A1:AA63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7317,6 +7317,99 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Delicadezas Españolas</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Delicadezas Españolas</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>39367</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala, Guatemala</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>2da Calle 18-49 Vista Hermosa 1,  Zona 15</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>01015</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delicadezasespanolas.com</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>delicadezas.espanolas2019@gmail.com</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>+502 2202 7400</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Delicadezas-Españolas-203834788932</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delicadezas_espanolas/</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>Abel Paniagua</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abel-paniagua-7010b5195</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Guatemala.xlsx
+++ b/BWI/bestwine_output/bestwine_Guatemala.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA63"/>
+  <dimension ref="A1:AA64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7410,6 +7410,99 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Delicadezas Españolas</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Delicadezas Españolas</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>39367</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala, Guatemala</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>2da Calle 18-49 Vista Hermosa 1,  Zona 15</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>01015</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delicadezasespanolas.com</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>delicadezas.espanolas2019@gmail.com</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>+502 2202 7400</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Delicadezas-Españolas-203834788932</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delicadezas_espanolas/</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>Abel Paniagua</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abel-paniagua-7010b5195</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Guatemala.xlsx
+++ b/BWI/bestwine_output/bestwine_Guatemala.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA64"/>
+  <dimension ref="A1:AA65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7503,6 +7503,99 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Delicadezas Españolas</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Delicadezas Españolas</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>39367</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala, Guatemala</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>2da Calle 18-49 Vista Hermosa 1,  Zona 15</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>01015</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delicadezasespanolas.com</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>delicadezas.espanolas2019@gmail.com</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>+502 2202 7400</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Delicadezas-Españolas-203834788932</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delicadezas_espanolas/</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>Abel Paniagua</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abel-paniagua-7010b5195</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
